--- a/results_minsup_ESBL/minsup_0_001/rep7/tab_recap_itemsets_0.95.xlsx
+++ b/results_minsup_ESBL/minsup_0_001/rep7/tab_recap_itemsets_0.95.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t xml:space="preserve">dataset</t>
   </si>
@@ -36,6 +36,15 @@
   </si>
   <si>
     <t xml:space="preserve">2018_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021_BLSE</t>
   </si>
   <si>
     <t xml:space="preserve">2022_BLSE</t>
@@ -418,21 +427,90 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>626202</v>
+        <v>556510</v>
       </c>
       <c r="C3" t="n">
-        <v>5200</v>
+        <v>5638</v>
       </c>
       <c r="D3" t="n">
-        <v>6.37</v>
+        <v>6.18</v>
       </c>
       <c r="E3" t="n">
         <v>11</v>
       </c>
       <c r="F3" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>549731</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5617</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="n">
+        <v>745181</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4958</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="n">
+        <v>626202</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5136</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="E6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F6" t="n">
         <v>4.11</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G6" t="n">
         <v>7</v>
       </c>
     </row>
